--- a/data/employees/EMP059/AST-EMP059-06.xlsx
+++ b/data/employees/EMP059/AST-EMP059-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System Resource Utilization" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,166 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>System Resource Utilization - Drew Kim (IT)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Drew Kim | Role: Lead | Location: Portland | Date: 2025-03-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>94</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>68</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Server</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>CPU %</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Memory %</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Disk %</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Network (Mbps)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROD-APP-01</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>67</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-W04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PROD-SQL-02</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>58</v>
-      </c>
-      <c r="C6" t="n">
-        <v>81</v>
-      </c>
-      <c r="D6" t="n">
-        <v>88</v>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-W05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>91</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WARNING</t>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV-WEB-01</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>40</v>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-W06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEST-API-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C8" t="n">
-        <v>52</v>
-      </c>
-      <c r="D8" t="n">
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-W07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>94</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>79</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>66</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>98</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>91</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>76</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>66</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>88</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>87</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>98</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>62</v>
       </c>
-      <c r="E8" t="n">
-        <v>450</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>70</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>99</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>70</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>72</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp059 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>71</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP059</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP059 contributes to ast emp059 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>